--- a/database/PeptideDatabase-70_mv_F427Y_guesthost_peptides.xlsx
+++ b/database/PeptideDatabase-70_mv_F427Y_guesthost_peptides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bakrantz/Documents/python/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641CA8AA-C99A-BA48-84A7-59FEA29C7D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF4FE8-BA44-7E43-A094-0B89DEDC99AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{771C88DF-88B2-E348-BE11-2567F4397102}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="369">
   <si>
     <t>guesthost_Ala</t>
   </si>
@@ -1126,6 +1126,21 @@
   </si>
   <si>
     <t>11826002-guesthost_Ala-70_mV-F427Y-400_Hz-downsampled-rpt_6.csv</t>
+  </si>
+  <si>
+    <t>ph_cis</t>
+  </si>
+  <si>
+    <t>ph_trans</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>salt_conc</t>
+  </si>
+  <si>
+    <t>KCl</t>
   </si>
 </sst>
 </file>
@@ -2023,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB02983-7886-F046-AB34-426E7E084EE9}">
-  <dimension ref="A1:Y121"/>
+  <dimension ref="A1:AC121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
@@ -2036,14 +2051,18 @@
     <col min="9" max="9" width="14.5" customWidth="1"/>
     <col min="10" max="10" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5" customWidth="1"/>
-    <col min="15" max="15" width="62" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="62" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -2078,21 +2097,33 @@
         <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1"/>
-      <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X1" s="1"/>
+      <c r="AC1" s="1"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2126,16 +2157,28 @@
         <v>25</v>
       </c>
       <c r="L2">
+        <v>5.6</v>
+      </c>
+      <c r="M2">
+        <v>5.6</v>
+      </c>
+      <c r="N2" t="s">
+        <v>368</v>
+      </c>
+      <c r="O2">
+        <v>0.1</v>
+      </c>
+      <c r="P2">
         <v>20</v>
       </c>
-      <c r="M2">
+      <c r="Q2">
         <v>600</v>
       </c>
-      <c r="O2" t="s">
+      <c r="S2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2169,16 +2212,28 @@
         <v>25</v>
       </c>
       <c r="L3">
+        <v>5.6</v>
+      </c>
+      <c r="M3">
+        <v>5.6</v>
+      </c>
+      <c r="N3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O3">
+        <v>0.1</v>
+      </c>
+      <c r="P3">
         <v>20</v>
       </c>
-      <c r="M3">
+      <c r="Q3">
         <v>600</v>
       </c>
-      <c r="O3" t="s">
+      <c r="S3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -2212,16 +2267,28 @@
         <v>25</v>
       </c>
       <c r="L4">
+        <v>5.6</v>
+      </c>
+      <c r="M4">
+        <v>5.6</v>
+      </c>
+      <c r="N4" t="s">
+        <v>368</v>
+      </c>
+      <c r="O4">
+        <v>0.1</v>
+      </c>
+      <c r="P4">
         <v>20</v>
       </c>
-      <c r="M4">
+      <c r="Q4">
         <v>600</v>
       </c>
-      <c r="O4" t="s">
+      <c r="S4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2255,16 +2322,28 @@
         <v>25</v>
       </c>
       <c r="L5">
+        <v>5.6</v>
+      </c>
+      <c r="M5">
+        <v>5.6</v>
+      </c>
+      <c r="N5" t="s">
+        <v>368</v>
+      </c>
+      <c r="O5">
+        <v>0.1</v>
+      </c>
+      <c r="P5">
         <v>20</v>
       </c>
-      <c r="M5">
+      <c r="Q5">
         <v>600</v>
       </c>
-      <c r="O5" t="s">
+      <c r="S5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -2298,16 +2377,28 @@
         <v>25</v>
       </c>
       <c r="L6">
+        <v>5.6</v>
+      </c>
+      <c r="M6">
+        <v>5.6</v>
+      </c>
+      <c r="N6" t="s">
+        <v>368</v>
+      </c>
+      <c r="O6">
+        <v>0.1</v>
+      </c>
+      <c r="P6">
         <v>20</v>
       </c>
-      <c r="M6">
+      <c r="Q6">
         <v>600</v>
       </c>
-      <c r="O6" t="s">
+      <c r="S6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -2341,16 +2432,28 @@
         <v>25</v>
       </c>
       <c r="L7">
+        <v>5.6</v>
+      </c>
+      <c r="M7">
+        <v>5.6</v>
+      </c>
+      <c r="N7" t="s">
+        <v>368</v>
+      </c>
+      <c r="O7">
+        <v>0.1</v>
+      </c>
+      <c r="P7">
         <v>20</v>
       </c>
-      <c r="M7">
+      <c r="Q7">
         <v>600</v>
       </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -2384,16 +2487,28 @@
         <v>25</v>
       </c>
       <c r="L8">
+        <v>5.6</v>
+      </c>
+      <c r="M8">
+        <v>5.6</v>
+      </c>
+      <c r="N8" t="s">
+        <v>368</v>
+      </c>
+      <c r="O8">
+        <v>0.1</v>
+      </c>
+      <c r="P8">
         <v>20</v>
       </c>
-      <c r="M8">
+      <c r="Q8">
         <v>600</v>
       </c>
-      <c r="O8" t="s">
+      <c r="S8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2427,16 +2542,28 @@
         <v>25</v>
       </c>
       <c r="L9">
+        <v>5.6</v>
+      </c>
+      <c r="M9">
+        <v>5.6</v>
+      </c>
+      <c r="N9" t="s">
+        <v>368</v>
+      </c>
+      <c r="O9">
+        <v>0.1</v>
+      </c>
+      <c r="P9">
         <v>20</v>
       </c>
-      <c r="M9">
+      <c r="Q9">
         <v>600</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -2470,16 +2597,28 @@
         <v>25</v>
       </c>
       <c r="L10">
+        <v>5.6</v>
+      </c>
+      <c r="M10">
+        <v>5.6</v>
+      </c>
+      <c r="N10" t="s">
+        <v>368</v>
+      </c>
+      <c r="O10">
+        <v>0.1</v>
+      </c>
+      <c r="P10">
         <v>20</v>
       </c>
-      <c r="M10">
+      <c r="Q10">
         <v>600</v>
       </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -2513,16 +2652,28 @@
         <v>25</v>
       </c>
       <c r="L11">
+        <v>5.6</v>
+      </c>
+      <c r="M11">
+        <v>5.6</v>
+      </c>
+      <c r="N11" t="s">
+        <v>368</v>
+      </c>
+      <c r="O11">
+        <v>0.1</v>
+      </c>
+      <c r="P11">
         <v>20</v>
       </c>
-      <c r="M11">
+      <c r="Q11">
         <v>600</v>
       </c>
-      <c r="O11" t="s">
+      <c r="S11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -2556,16 +2707,28 @@
         <v>25</v>
       </c>
       <c r="L12">
+        <v>5.6</v>
+      </c>
+      <c r="M12">
+        <v>5.6</v>
+      </c>
+      <c r="N12" t="s">
+        <v>368</v>
+      </c>
+      <c r="O12">
+        <v>0.1</v>
+      </c>
+      <c r="P12">
         <v>20</v>
       </c>
-      <c r="M12">
+      <c r="Q12">
         <v>600</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -2599,16 +2762,28 @@
         <v>25</v>
       </c>
       <c r="L13">
+        <v>5.6</v>
+      </c>
+      <c r="M13">
+        <v>5.6</v>
+      </c>
+      <c r="N13" t="s">
+        <v>368</v>
+      </c>
+      <c r="O13">
+        <v>0.1</v>
+      </c>
+      <c r="P13">
         <v>20</v>
       </c>
-      <c r="M13">
+      <c r="Q13">
         <v>600</v>
       </c>
-      <c r="O13" t="s">
+      <c r="S13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -2642,16 +2817,28 @@
         <v>25</v>
       </c>
       <c r="L14">
+        <v>5.6</v>
+      </c>
+      <c r="M14">
+        <v>5.6</v>
+      </c>
+      <c r="N14" t="s">
+        <v>368</v>
+      </c>
+      <c r="O14">
+        <v>0.1</v>
+      </c>
+      <c r="P14">
         <v>20</v>
       </c>
-      <c r="M14">
+      <c r="Q14">
         <v>600</v>
       </c>
-      <c r="O14" t="s">
+      <c r="S14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -2685,16 +2872,28 @@
         <v>25</v>
       </c>
       <c r="L15">
+        <v>5.6</v>
+      </c>
+      <c r="M15">
+        <v>5.6</v>
+      </c>
+      <c r="N15" t="s">
+        <v>368</v>
+      </c>
+      <c r="O15">
+        <v>0.1</v>
+      </c>
+      <c r="P15">
         <v>20</v>
       </c>
-      <c r="M15">
+      <c r="Q15">
         <v>600</v>
       </c>
-      <c r="O15" t="s">
+      <c r="S15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -2728,16 +2927,28 @@
         <v>25</v>
       </c>
       <c r="L16">
+        <v>5.6</v>
+      </c>
+      <c r="M16">
+        <v>5.6</v>
+      </c>
+      <c r="N16" t="s">
+        <v>368</v>
+      </c>
+      <c r="O16">
+        <v>0.1</v>
+      </c>
+      <c r="P16">
         <v>20</v>
       </c>
-      <c r="M16">
+      <c r="Q16">
         <v>400</v>
       </c>
-      <c r="O16" t="s">
+      <c r="S16" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -2771,16 +2982,28 @@
         <v>25</v>
       </c>
       <c r="L17">
+        <v>5.6</v>
+      </c>
+      <c r="M17">
+        <v>5.6</v>
+      </c>
+      <c r="N17" t="s">
+        <v>368</v>
+      </c>
+      <c r="O17">
+        <v>0.1</v>
+      </c>
+      <c r="P17">
         <v>20</v>
       </c>
-      <c r="M17">
+      <c r="Q17">
         <v>400</v>
       </c>
-      <c r="O17" t="s">
+      <c r="S17" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -2814,16 +3037,28 @@
         <v>25</v>
       </c>
       <c r="L18">
+        <v>5.6</v>
+      </c>
+      <c r="M18">
+        <v>5.6</v>
+      </c>
+      <c r="N18" t="s">
+        <v>368</v>
+      </c>
+      <c r="O18">
+        <v>0.1</v>
+      </c>
+      <c r="P18">
         <v>20</v>
       </c>
-      <c r="M18">
+      <c r="Q18">
         <v>400</v>
       </c>
-      <c r="O18" t="s">
+      <c r="S18" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -2857,16 +3092,28 @@
         <v>25</v>
       </c>
       <c r="L19">
+        <v>5.6</v>
+      </c>
+      <c r="M19">
+        <v>5.6</v>
+      </c>
+      <c r="N19" t="s">
+        <v>368</v>
+      </c>
+      <c r="O19">
+        <v>0.1</v>
+      </c>
+      <c r="P19">
         <v>20</v>
       </c>
-      <c r="M19">
+      <c r="Q19">
         <v>400</v>
       </c>
-      <c r="O19" t="s">
+      <c r="S19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -2900,16 +3147,28 @@
         <v>25</v>
       </c>
       <c r="L20">
+        <v>5.6</v>
+      </c>
+      <c r="M20">
+        <v>5.6</v>
+      </c>
+      <c r="N20" t="s">
+        <v>368</v>
+      </c>
+      <c r="O20">
+        <v>0.1</v>
+      </c>
+      <c r="P20">
         <v>20</v>
       </c>
-      <c r="M20">
+      <c r="Q20">
         <v>400</v>
       </c>
-      <c r="O20" t="s">
+      <c r="S20" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -2943,16 +3202,28 @@
         <v>25</v>
       </c>
       <c r="L21">
+        <v>5.6</v>
+      </c>
+      <c r="M21">
+        <v>5.6</v>
+      </c>
+      <c r="N21" t="s">
+        <v>368</v>
+      </c>
+      <c r="O21">
+        <v>0.1</v>
+      </c>
+      <c r="P21">
         <v>20</v>
       </c>
-      <c r="M21">
+      <c r="Q21">
         <v>400</v>
       </c>
-      <c r="O21" t="s">
+      <c r="S21" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -2986,16 +3257,28 @@
         <v>25</v>
       </c>
       <c r="L22">
+        <v>5.6</v>
+      </c>
+      <c r="M22">
+        <v>5.6</v>
+      </c>
+      <c r="N22" t="s">
+        <v>368</v>
+      </c>
+      <c r="O22">
+        <v>0.1</v>
+      </c>
+      <c r="P22">
         <v>20</v>
       </c>
-      <c r="M22">
+      <c r="Q22">
         <v>400</v>
       </c>
-      <c r="O22" t="s">
+      <c r="S22" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -3029,16 +3312,28 @@
         <v>25</v>
       </c>
       <c r="L23">
+        <v>5.6</v>
+      </c>
+      <c r="M23">
+        <v>5.6</v>
+      </c>
+      <c r="N23" t="s">
+        <v>368</v>
+      </c>
+      <c r="O23">
+        <v>0.1</v>
+      </c>
+      <c r="P23">
         <v>20</v>
       </c>
-      <c r="M23">
+      <c r="Q23">
         <v>400</v>
       </c>
-      <c r="O23" t="s">
+      <c r="S23" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -3072,16 +3367,28 @@
         <v>25</v>
       </c>
       <c r="L24">
+        <v>5.6</v>
+      </c>
+      <c r="M24">
+        <v>5.6</v>
+      </c>
+      <c r="N24" t="s">
+        <v>368</v>
+      </c>
+      <c r="O24">
+        <v>0.1</v>
+      </c>
+      <c r="P24">
         <v>20</v>
       </c>
-      <c r="M24">
+      <c r="Q24">
         <v>400</v>
       </c>
-      <c r="O24" t="s">
+      <c r="S24" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -3115,16 +3422,28 @@
         <v>25</v>
       </c>
       <c r="L25">
+        <v>5.6</v>
+      </c>
+      <c r="M25">
+        <v>5.6</v>
+      </c>
+      <c r="N25" t="s">
+        <v>368</v>
+      </c>
+      <c r="O25">
+        <v>0.1</v>
+      </c>
+      <c r="P25">
         <v>20</v>
       </c>
-      <c r="M25">
+      <c r="Q25">
         <v>400</v>
       </c>
-      <c r="O25" t="s">
+      <c r="S25" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -3158,16 +3477,28 @@
         <v>25</v>
       </c>
       <c r="L26">
+        <v>5.6</v>
+      </c>
+      <c r="M26">
+        <v>5.6</v>
+      </c>
+      <c r="N26" t="s">
+        <v>368</v>
+      </c>
+      <c r="O26">
+        <v>0.1</v>
+      </c>
+      <c r="P26">
         <v>20</v>
       </c>
-      <c r="M26">
+      <c r="Q26">
         <v>400</v>
       </c>
-      <c r="O26" t="s">
+      <c r="S26" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -3201,16 +3532,28 @@
         <v>25</v>
       </c>
       <c r="L27">
+        <v>5.6</v>
+      </c>
+      <c r="M27">
+        <v>5.6</v>
+      </c>
+      <c r="N27" t="s">
+        <v>368</v>
+      </c>
+      <c r="O27">
+        <v>0.1</v>
+      </c>
+      <c r="P27">
         <v>20</v>
       </c>
-      <c r="M27">
+      <c r="Q27">
         <v>400</v>
       </c>
-      <c r="O27" t="s">
+      <c r="S27" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -3244,16 +3587,28 @@
         <v>25</v>
       </c>
       <c r="L28">
+        <v>5.6</v>
+      </c>
+      <c r="M28">
+        <v>5.6</v>
+      </c>
+      <c r="N28" t="s">
+        <v>368</v>
+      </c>
+      <c r="O28">
+        <v>0.1</v>
+      </c>
+      <c r="P28">
         <v>20</v>
       </c>
-      <c r="M28">
+      <c r="Q28">
         <v>400</v>
       </c>
-      <c r="O28" t="s">
+      <c r="S28" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -3287,16 +3642,28 @@
         <v>25</v>
       </c>
       <c r="L29">
+        <v>5.6</v>
+      </c>
+      <c r="M29">
+        <v>5.6</v>
+      </c>
+      <c r="N29" t="s">
+        <v>368</v>
+      </c>
+      <c r="O29">
+        <v>0.1</v>
+      </c>
+      <c r="P29">
         <v>20</v>
       </c>
-      <c r="M29">
+      <c r="Q29">
         <v>400</v>
       </c>
-      <c r="O29" t="s">
+      <c r="S29" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>1</v>
       </c>
@@ -3329,17 +3696,29 @@
       <c r="K30" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30">
+        <v>5.6</v>
+      </c>
+      <c r="M30">
+        <v>5.6</v>
+      </c>
+      <c r="N30" t="s">
+        <v>368</v>
+      </c>
+      <c r="O30">
+        <v>0.1</v>
+      </c>
+      <c r="P30" s="5">
         <v>20</v>
       </c>
-      <c r="M30" s="5">
+      <c r="Q30" s="5">
         <v>500</v>
       </c>
-      <c r="O30" s="5" t="s">
+      <c r="S30" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>1</v>
       </c>
@@ -3372,17 +3751,29 @@
       <c r="K31" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="5">
+      <c r="L31">
+        <v>5.6</v>
+      </c>
+      <c r="M31">
+        <v>5.6</v>
+      </c>
+      <c r="N31" t="s">
+        <v>368</v>
+      </c>
+      <c r="O31">
+        <v>0.1</v>
+      </c>
+      <c r="P31" s="5">
         <v>20</v>
       </c>
-      <c r="M31" s="5">
+      <c r="Q31" s="5">
         <v>500</v>
       </c>
-      <c r="O31" s="5" t="s">
+      <c r="S31" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>1</v>
       </c>
@@ -3415,17 +3806,29 @@
       <c r="K32" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32">
+        <v>5.6</v>
+      </c>
+      <c r="M32">
+        <v>5.6</v>
+      </c>
+      <c r="N32" t="s">
+        <v>368</v>
+      </c>
+      <c r="O32">
+        <v>0.1</v>
+      </c>
+      <c r="P32" s="5">
         <v>20</v>
       </c>
-      <c r="M32" s="5">
+      <c r="Q32" s="5">
         <v>500</v>
       </c>
-      <c r="O32" s="5" t="s">
+      <c r="S32" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>1</v>
       </c>
@@ -3458,17 +3861,29 @@
       <c r="K33" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L33">
+        <v>5.6</v>
+      </c>
+      <c r="M33">
+        <v>5.6</v>
+      </c>
+      <c r="N33" t="s">
+        <v>368</v>
+      </c>
+      <c r="O33">
+        <v>0.1</v>
+      </c>
+      <c r="P33" s="5">
         <v>20</v>
       </c>
-      <c r="M33" s="5">
+      <c r="Q33" s="5">
         <v>500</v>
       </c>
-      <c r="O33" s="5" t="s">
+      <c r="S33" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>1</v>
       </c>
@@ -3501,17 +3916,29 @@
       <c r="K34" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34">
+        <v>5.6</v>
+      </c>
+      <c r="M34">
+        <v>5.6</v>
+      </c>
+      <c r="N34" t="s">
+        <v>368</v>
+      </c>
+      <c r="O34">
+        <v>0.1</v>
+      </c>
+      <c r="P34" s="5">
         <v>20</v>
       </c>
-      <c r="M34" s="5">
+      <c r="Q34" s="5">
         <v>500</v>
       </c>
-      <c r="O34" s="5" t="s">
+      <c r="S34" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>1</v>
       </c>
@@ -3544,17 +3971,29 @@
       <c r="K35" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L35">
+        <v>5.6</v>
+      </c>
+      <c r="M35">
+        <v>5.6</v>
+      </c>
+      <c r="N35" t="s">
+        <v>368</v>
+      </c>
+      <c r="O35">
+        <v>0.1</v>
+      </c>
+      <c r="P35" s="5">
         <v>20</v>
       </c>
-      <c r="M35" s="5">
+      <c r="Q35" s="5">
         <v>500</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="S35" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>1</v>
       </c>
@@ -3587,17 +4026,29 @@
       <c r="K36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36">
+        <v>5.6</v>
+      </c>
+      <c r="M36">
+        <v>5.6</v>
+      </c>
+      <c r="N36" t="s">
+        <v>368</v>
+      </c>
+      <c r="O36">
+        <v>0.1</v>
+      </c>
+      <c r="P36" s="5">
         <v>20</v>
       </c>
-      <c r="M36" s="5">
+      <c r="Q36" s="5">
         <v>500</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="S36" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>1</v>
       </c>
@@ -3630,17 +4081,29 @@
       <c r="K37" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L37" s="5">
+      <c r="L37">
+        <v>5.6</v>
+      </c>
+      <c r="M37">
+        <v>5.6</v>
+      </c>
+      <c r="N37" t="s">
+        <v>368</v>
+      </c>
+      <c r="O37">
+        <v>0.1</v>
+      </c>
+      <c r="P37" s="5">
         <v>20</v>
       </c>
-      <c r="M37" s="5">
+      <c r="Q37" s="5">
         <v>500</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="S37" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>1</v>
       </c>
@@ -3673,17 +4136,29 @@
       <c r="K38" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="5">
+      <c r="L38">
+        <v>5.6</v>
+      </c>
+      <c r="M38">
+        <v>5.6</v>
+      </c>
+      <c r="N38" t="s">
+        <v>368</v>
+      </c>
+      <c r="O38">
+        <v>0.1</v>
+      </c>
+      <c r="P38" s="5">
         <v>20</v>
       </c>
-      <c r="M38" s="5">
+      <c r="Q38" s="5">
         <v>500</v>
       </c>
-      <c r="O38" s="5" t="s">
+      <c r="S38" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>1</v>
       </c>
@@ -3716,17 +4191,29 @@
       <c r="K39" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="5">
+      <c r="L39">
+        <v>5.6</v>
+      </c>
+      <c r="M39">
+        <v>5.6</v>
+      </c>
+      <c r="N39" t="s">
+        <v>368</v>
+      </c>
+      <c r="O39">
+        <v>0.1</v>
+      </c>
+      <c r="P39" s="5">
         <v>20</v>
       </c>
-      <c r="M39" s="5">
+      <c r="Q39" s="5">
         <v>400</v>
       </c>
-      <c r="O39" s="5" t="s">
+      <c r="S39" s="5" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>1</v>
       </c>
@@ -3759,17 +4246,29 @@
       <c r="K40" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L40" s="5">
+      <c r="L40">
+        <v>5.6</v>
+      </c>
+      <c r="M40">
+        <v>5.6</v>
+      </c>
+      <c r="N40" t="s">
+        <v>368</v>
+      </c>
+      <c r="O40">
+        <v>0.1</v>
+      </c>
+      <c r="P40" s="5">
         <v>20</v>
       </c>
-      <c r="M40" s="5">
+      <c r="Q40" s="5">
         <v>400</v>
       </c>
-      <c r="O40" s="5" t="s">
+      <c r="S40" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>1</v>
       </c>
@@ -3802,17 +4301,29 @@
       <c r="K41" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L41" s="5">
+      <c r="L41">
+        <v>5.6</v>
+      </c>
+      <c r="M41">
+        <v>5.6</v>
+      </c>
+      <c r="N41" t="s">
+        <v>368</v>
+      </c>
+      <c r="O41">
+        <v>0.1</v>
+      </c>
+      <c r="P41" s="5">
         <v>20</v>
       </c>
-      <c r="M41" s="5">
+      <c r="Q41" s="5">
         <v>400</v>
       </c>
-      <c r="O41" s="5" t="s">
+      <c r="S41" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>1</v>
       </c>
@@ -3845,17 +4356,29 @@
       <c r="K42" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42">
+        <v>5.6</v>
+      </c>
+      <c r="M42">
+        <v>5.6</v>
+      </c>
+      <c r="N42" t="s">
+        <v>368</v>
+      </c>
+      <c r="O42">
+        <v>0.1</v>
+      </c>
+      <c r="P42" s="5">
         <v>20</v>
       </c>
-      <c r="M42" s="5">
+      <c r="Q42" s="5">
         <v>400</v>
       </c>
-      <c r="O42" s="5" t="s">
+      <c r="S42" s="5" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>1</v>
       </c>
@@ -3888,17 +4411,29 @@
       <c r="K43" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43">
+        <v>5.6</v>
+      </c>
+      <c r="M43">
+        <v>5.6</v>
+      </c>
+      <c r="N43" t="s">
+        <v>368</v>
+      </c>
+      <c r="O43">
+        <v>0.1</v>
+      </c>
+      <c r="P43" s="5">
         <v>20</v>
       </c>
-      <c r="M43" s="5">
+      <c r="Q43" s="5">
         <v>400</v>
       </c>
-      <c r="O43" s="5" t="s">
+      <c r="S43" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>1</v>
       </c>
@@ -3931,17 +4466,29 @@
       <c r="K44" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L44" s="5">
+      <c r="L44">
+        <v>5.6</v>
+      </c>
+      <c r="M44">
+        <v>5.6</v>
+      </c>
+      <c r="N44" t="s">
+        <v>368</v>
+      </c>
+      <c r="O44">
+        <v>0.1</v>
+      </c>
+      <c r="P44" s="5">
         <v>20</v>
       </c>
-      <c r="M44" s="5">
+      <c r="Q44" s="5">
         <v>400</v>
       </c>
-      <c r="O44" s="5" t="s">
+      <c r="S44" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>1</v>
       </c>
@@ -3974,17 +4521,29 @@
       <c r="K45" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="5">
+      <c r="L45">
+        <v>5.6</v>
+      </c>
+      <c r="M45">
+        <v>5.6</v>
+      </c>
+      <c r="N45" t="s">
+        <v>368</v>
+      </c>
+      <c r="O45">
+        <v>0.1</v>
+      </c>
+      <c r="P45" s="5">
         <v>20</v>
       </c>
-      <c r="M45" s="5">
+      <c r="Q45" s="5">
         <v>400</v>
       </c>
-      <c r="O45" s="5" t="s">
+      <c r="S45" s="5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>1</v>
       </c>
@@ -4017,17 +4576,29 @@
       <c r="K46" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L46" s="5">
+      <c r="L46">
+        <v>5.6</v>
+      </c>
+      <c r="M46">
+        <v>5.6</v>
+      </c>
+      <c r="N46" t="s">
+        <v>368</v>
+      </c>
+      <c r="O46">
+        <v>0.1</v>
+      </c>
+      <c r="P46" s="5">
         <v>20</v>
       </c>
-      <c r="M46" s="5">
+      <c r="Q46" s="5">
         <v>400</v>
       </c>
-      <c r="O46" s="5" t="s">
+      <c r="S46" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>1</v>
       </c>
@@ -4060,17 +4631,29 @@
       <c r="K47" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L47" s="5">
+      <c r="L47">
+        <v>5.6</v>
+      </c>
+      <c r="M47">
+        <v>5.6</v>
+      </c>
+      <c r="N47" t="s">
+        <v>368</v>
+      </c>
+      <c r="O47">
+        <v>0.1</v>
+      </c>
+      <c r="P47" s="5">
         <v>20</v>
       </c>
-      <c r="M47" s="5">
+      <c r="Q47" s="5">
         <v>400</v>
       </c>
-      <c r="O47" s="5" t="s">
+      <c r="S47" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>2</v>
       </c>
@@ -4104,16 +4687,28 @@
         <v>25</v>
       </c>
       <c r="L48">
+        <v>5.6</v>
+      </c>
+      <c r="M48">
+        <v>5.6</v>
+      </c>
+      <c r="N48" t="s">
+        <v>368</v>
+      </c>
+      <c r="O48">
+        <v>0.1</v>
+      </c>
+      <c r="P48">
         <v>19</v>
       </c>
-      <c r="M48">
+      <c r="Q48">
         <v>500</v>
       </c>
-      <c r="O48" t="s">
+      <c r="S48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>2</v>
       </c>
@@ -4147,16 +4742,28 @@
         <v>25</v>
       </c>
       <c r="L49">
+        <v>5.6</v>
+      </c>
+      <c r="M49">
+        <v>5.6</v>
+      </c>
+      <c r="N49" t="s">
+        <v>368</v>
+      </c>
+      <c r="O49">
+        <v>0.1</v>
+      </c>
+      <c r="P49">
         <v>19</v>
       </c>
-      <c r="M49">
+      <c r="Q49">
         <v>500</v>
       </c>
-      <c r="O49" t="s">
+      <c r="S49" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>2</v>
       </c>
@@ -4190,16 +4797,28 @@
         <v>25</v>
       </c>
       <c r="L50">
+        <v>5.6</v>
+      </c>
+      <c r="M50">
+        <v>5.6</v>
+      </c>
+      <c r="N50" t="s">
+        <v>368</v>
+      </c>
+      <c r="O50">
+        <v>0.1</v>
+      </c>
+      <c r="P50">
         <v>19</v>
       </c>
-      <c r="M50">
+      <c r="Q50">
         <v>500</v>
       </c>
-      <c r="O50" t="s">
+      <c r="S50" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>2</v>
       </c>
@@ -4233,16 +4852,28 @@
         <v>25</v>
       </c>
       <c r="L51">
+        <v>5.6</v>
+      </c>
+      <c r="M51">
+        <v>5.6</v>
+      </c>
+      <c r="N51" t="s">
+        <v>368</v>
+      </c>
+      <c r="O51">
+        <v>0.1</v>
+      </c>
+      <c r="P51">
         <v>19</v>
       </c>
-      <c r="M51">
+      <c r="Q51">
         <v>500</v>
       </c>
-      <c r="O51" t="s">
+      <c r="S51" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>2</v>
       </c>
@@ -4276,16 +4907,28 @@
         <v>25</v>
       </c>
       <c r="L52">
+        <v>5.6</v>
+      </c>
+      <c r="M52">
+        <v>5.6</v>
+      </c>
+      <c r="N52" t="s">
+        <v>368</v>
+      </c>
+      <c r="O52">
+        <v>0.1</v>
+      </c>
+      <c r="P52">
         <v>19</v>
       </c>
-      <c r="M52">
+      <c r="Q52">
         <v>500</v>
       </c>
-      <c r="O52" t="s">
+      <c r="S52" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>2</v>
       </c>
@@ -4319,16 +4962,28 @@
         <v>25</v>
       </c>
       <c r="L53">
+        <v>5.6</v>
+      </c>
+      <c r="M53">
+        <v>5.6</v>
+      </c>
+      <c r="N53" t="s">
+        <v>368</v>
+      </c>
+      <c r="O53">
+        <v>0.1</v>
+      </c>
+      <c r="P53">
         <v>19</v>
       </c>
-      <c r="M53">
+      <c r="Q53">
         <v>500</v>
       </c>
-      <c r="O53" t="s">
+      <c r="S53" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -4362,16 +5017,28 @@
         <v>25</v>
       </c>
       <c r="L54">
+        <v>5.6</v>
+      </c>
+      <c r="M54">
+        <v>5.6</v>
+      </c>
+      <c r="N54" t="s">
+        <v>368</v>
+      </c>
+      <c r="O54">
+        <v>0.1</v>
+      </c>
+      <c r="P54">
         <v>19</v>
       </c>
-      <c r="M54">
+      <c r="Q54">
         <v>500</v>
       </c>
-      <c r="O54" t="s">
+      <c r="S54" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -4405,16 +5072,28 @@
         <v>25</v>
       </c>
       <c r="L55">
+        <v>5.6</v>
+      </c>
+      <c r="M55">
+        <v>5.6</v>
+      </c>
+      <c r="N55" t="s">
+        <v>368</v>
+      </c>
+      <c r="O55">
+        <v>0.1</v>
+      </c>
+      <c r="P55">
         <v>19</v>
       </c>
-      <c r="M55">
+      <c r="Q55">
         <v>500</v>
       </c>
-      <c r="O55" t="s">
+      <c r="S55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -4448,16 +5127,28 @@
         <v>25</v>
       </c>
       <c r="L56">
+        <v>5.6</v>
+      </c>
+      <c r="M56">
+        <v>5.6</v>
+      </c>
+      <c r="N56" t="s">
+        <v>368</v>
+      </c>
+      <c r="O56">
+        <v>0.1</v>
+      </c>
+      <c r="P56">
         <v>19</v>
       </c>
-      <c r="M56">
+      <c r="Q56">
         <v>500</v>
       </c>
-      <c r="O56" t="s">
+      <c r="S56" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>2</v>
       </c>
@@ -4491,16 +5182,28 @@
         <v>25</v>
       </c>
       <c r="L57">
+        <v>5.6</v>
+      </c>
+      <c r="M57">
+        <v>5.6</v>
+      </c>
+      <c r="N57" t="s">
+        <v>368</v>
+      </c>
+      <c r="O57">
+        <v>0.1</v>
+      </c>
+      <c r="P57">
         <v>19</v>
       </c>
-      <c r="M57">
+      <c r="Q57">
         <v>500</v>
       </c>
-      <c r="O57" t="s">
+      <c r="S57" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>2</v>
       </c>
@@ -4534,16 +5237,28 @@
         <v>25</v>
       </c>
       <c r="L58">
+        <v>5.6</v>
+      </c>
+      <c r="M58">
+        <v>5.6</v>
+      </c>
+      <c r="N58" t="s">
+        <v>368</v>
+      </c>
+      <c r="O58">
+        <v>0.1</v>
+      </c>
+      <c r="P58">
         <v>19</v>
       </c>
-      <c r="M58">
+      <c r="Q58">
         <v>500</v>
       </c>
-      <c r="O58" t="s">
+      <c r="S58" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>2</v>
       </c>
@@ -4577,16 +5292,28 @@
         <v>25</v>
       </c>
       <c r="L59">
+        <v>5.6</v>
+      </c>
+      <c r="M59">
+        <v>5.6</v>
+      </c>
+      <c r="N59" t="s">
+        <v>368</v>
+      </c>
+      <c r="O59">
+        <v>0.1</v>
+      </c>
+      <c r="P59">
         <v>19</v>
       </c>
-      <c r="M59">
+      <c r="Q59">
         <v>500</v>
       </c>
-      <c r="O59" t="s">
+      <c r="S59" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>2</v>
       </c>
@@ -4620,16 +5347,28 @@
         <v>25</v>
       </c>
       <c r="L60">
+        <v>5.6</v>
+      </c>
+      <c r="M60">
+        <v>5.6</v>
+      </c>
+      <c r="N60" t="s">
+        <v>368</v>
+      </c>
+      <c r="O60">
+        <v>0.1</v>
+      </c>
+      <c r="P60">
         <v>19</v>
       </c>
-      <c r="M60">
+      <c r="Q60">
         <v>500</v>
       </c>
-      <c r="O60" t="s">
+      <c r="S60" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -4663,16 +5402,28 @@
         <v>25</v>
       </c>
       <c r="L61">
+        <v>5.6</v>
+      </c>
+      <c r="M61">
+        <v>5.6</v>
+      </c>
+      <c r="N61" t="s">
+        <v>368</v>
+      </c>
+      <c r="O61">
+        <v>0.1</v>
+      </c>
+      <c r="P61">
         <v>19</v>
       </c>
-      <c r="M61">
+      <c r="Q61">
         <v>500</v>
       </c>
-      <c r="O61" t="s">
+      <c r="S61" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -4706,16 +5457,28 @@
         <v>25</v>
       </c>
       <c r="L62">
+        <v>5.6</v>
+      </c>
+      <c r="M62">
+        <v>5.6</v>
+      </c>
+      <c r="N62" t="s">
+        <v>368</v>
+      </c>
+      <c r="O62">
+        <v>0.1</v>
+      </c>
+      <c r="P62">
         <v>19</v>
       </c>
-      <c r="M62">
+      <c r="Q62">
         <v>500</v>
       </c>
-      <c r="O62" t="s">
+      <c r="S62" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -4749,16 +5512,28 @@
         <v>25</v>
       </c>
       <c r="L63">
+        <v>5.6</v>
+      </c>
+      <c r="M63">
+        <v>5.6</v>
+      </c>
+      <c r="N63" t="s">
+        <v>368</v>
+      </c>
+      <c r="O63">
+        <v>0.1</v>
+      </c>
+      <c r="P63">
         <v>19</v>
       </c>
-      <c r="M63">
+      <c r="Q63">
         <v>400</v>
       </c>
-      <c r="O63" t="s">
+      <c r="S63" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -4792,16 +5567,28 @@
         <v>25</v>
       </c>
       <c r="L64">
+        <v>5.6</v>
+      </c>
+      <c r="M64">
+        <v>5.6</v>
+      </c>
+      <c r="N64" t="s">
+        <v>368</v>
+      </c>
+      <c r="O64">
+        <v>0.1</v>
+      </c>
+      <c r="P64">
         <v>19</v>
       </c>
-      <c r="M64">
+      <c r="Q64">
         <v>400</v>
       </c>
-      <c r="O64" t="s">
+      <c r="S64" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -4835,16 +5622,28 @@
         <v>25</v>
       </c>
       <c r="L65">
+        <v>5.6</v>
+      </c>
+      <c r="M65">
+        <v>5.6</v>
+      </c>
+      <c r="N65" t="s">
+        <v>368</v>
+      </c>
+      <c r="O65">
+        <v>0.1</v>
+      </c>
+      <c r="P65">
         <v>19</v>
       </c>
-      <c r="M65">
+      <c r="Q65">
         <v>400</v>
       </c>
-      <c r="O65" t="s">
+      <c r="S65" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -4878,16 +5677,28 @@
         <v>25</v>
       </c>
       <c r="L66">
+        <v>5.6</v>
+      </c>
+      <c r="M66">
+        <v>5.6</v>
+      </c>
+      <c r="N66" t="s">
+        <v>368</v>
+      </c>
+      <c r="O66">
+        <v>0.1</v>
+      </c>
+      <c r="P66">
         <v>19</v>
       </c>
-      <c r="M66">
+      <c r="Q66">
         <v>400</v>
       </c>
-      <c r="O66" t="s">
+      <c r="S66" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -4921,16 +5732,28 @@
         <v>25</v>
       </c>
       <c r="L67">
+        <v>5.6</v>
+      </c>
+      <c r="M67">
+        <v>5.6</v>
+      </c>
+      <c r="N67" t="s">
+        <v>368</v>
+      </c>
+      <c r="O67">
+        <v>0.1</v>
+      </c>
+      <c r="P67">
         <v>19</v>
       </c>
-      <c r="M67">
+      <c r="Q67">
         <v>400</v>
       </c>
-      <c r="O67" t="s">
+      <c r="S67" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>2</v>
       </c>
@@ -4964,16 +5787,28 @@
         <v>25</v>
       </c>
       <c r="L68">
+        <v>5.6</v>
+      </c>
+      <c r="M68">
+        <v>5.6</v>
+      </c>
+      <c r="N68" t="s">
+        <v>368</v>
+      </c>
+      <c r="O68">
+        <v>0.1</v>
+      </c>
+      <c r="P68">
         <v>19</v>
       </c>
-      <c r="M68">
+      <c r="Q68">
         <v>400</v>
       </c>
-      <c r="O68" t="s">
+      <c r="S68" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>2</v>
       </c>
@@ -5007,16 +5842,28 @@
         <v>25</v>
       </c>
       <c r="L69">
+        <v>5.6</v>
+      </c>
+      <c r="M69">
+        <v>5.6</v>
+      </c>
+      <c r="N69" t="s">
+        <v>368</v>
+      </c>
+      <c r="O69">
+        <v>0.1</v>
+      </c>
+      <c r="P69">
         <v>19</v>
       </c>
-      <c r="M69">
+      <c r="Q69">
         <v>400</v>
       </c>
-      <c r="O69" t="s">
+      <c r="S69" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -5050,16 +5897,28 @@
         <v>25</v>
       </c>
       <c r="L70">
+        <v>5.6</v>
+      </c>
+      <c r="M70">
+        <v>5.6</v>
+      </c>
+      <c r="N70" t="s">
+        <v>368</v>
+      </c>
+      <c r="O70">
+        <v>0.1</v>
+      </c>
+      <c r="P70">
         <v>19</v>
       </c>
-      <c r="M70">
+      <c r="Q70">
         <v>400</v>
       </c>
-      <c r="O70" t="s">
+      <c r="S70" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>2</v>
       </c>
@@ -5093,16 +5952,28 @@
         <v>25</v>
       </c>
       <c r="L71">
+        <v>5.6</v>
+      </c>
+      <c r="M71">
+        <v>5.6</v>
+      </c>
+      <c r="N71" t="s">
+        <v>368</v>
+      </c>
+      <c r="O71">
+        <v>0.1</v>
+      </c>
+      <c r="P71">
         <v>19</v>
       </c>
-      <c r="M71">
+      <c r="Q71">
         <v>400</v>
       </c>
-      <c r="O71" t="s">
+      <c r="S71" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -5136,16 +6007,28 @@
         <v>25</v>
       </c>
       <c r="L72">
+        <v>5.6</v>
+      </c>
+      <c r="M72">
+        <v>5.6</v>
+      </c>
+      <c r="N72" t="s">
+        <v>368</v>
+      </c>
+      <c r="O72">
+        <v>0.1</v>
+      </c>
+      <c r="P72">
         <v>19</v>
       </c>
-      <c r="M72">
+      <c r="Q72">
         <v>400</v>
       </c>
-      <c r="O72" t="s">
+      <c r="S72" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -5179,16 +6062,28 @@
         <v>25</v>
       </c>
       <c r="L73">
+        <v>5.6</v>
+      </c>
+      <c r="M73">
+        <v>5.6</v>
+      </c>
+      <c r="N73" t="s">
+        <v>368</v>
+      </c>
+      <c r="O73">
+        <v>0.1</v>
+      </c>
+      <c r="P73">
         <v>19</v>
       </c>
-      <c r="M73">
+      <c r="Q73">
         <v>400</v>
       </c>
-      <c r="O73" t="s">
+      <c r="S73" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -5222,16 +6117,28 @@
         <v>25</v>
       </c>
       <c r="L74">
+        <v>5.6</v>
+      </c>
+      <c r="M74">
+        <v>5.6</v>
+      </c>
+      <c r="N74" t="s">
+        <v>368</v>
+      </c>
+      <c r="O74">
+        <v>0.1</v>
+      </c>
+      <c r="P74">
         <v>19</v>
       </c>
-      <c r="M74">
+      <c r="Q74">
         <v>400</v>
       </c>
-      <c r="O74" t="s">
+      <c r="S74" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -5265,16 +6172,28 @@
         <v>25</v>
       </c>
       <c r="L75">
+        <v>5.6</v>
+      </c>
+      <c r="M75">
+        <v>5.6</v>
+      </c>
+      <c r="N75" t="s">
+        <v>368</v>
+      </c>
+      <c r="O75">
+        <v>0.1</v>
+      </c>
+      <c r="P75">
         <v>19</v>
       </c>
-      <c r="M75">
+      <c r="Q75">
         <v>400</v>
       </c>
-      <c r="O75" t="s">
+      <c r="S75" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -5308,16 +6227,28 @@
         <v>25</v>
       </c>
       <c r="L76">
+        <v>5.6</v>
+      </c>
+      <c r="M76">
+        <v>5.6</v>
+      </c>
+      <c r="N76" t="s">
+        <v>368</v>
+      </c>
+      <c r="O76">
+        <v>0.1</v>
+      </c>
+      <c r="P76">
         <v>19</v>
       </c>
-      <c r="M76">
+      <c r="Q76">
         <v>400</v>
       </c>
-      <c r="O76" t="s">
+      <c r="S76" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>2</v>
       </c>
@@ -5351,16 +6282,28 @@
         <v>25</v>
       </c>
       <c r="L77">
+        <v>5.6</v>
+      </c>
+      <c r="M77">
+        <v>5.6</v>
+      </c>
+      <c r="N77" t="s">
+        <v>368</v>
+      </c>
+      <c r="O77">
+        <v>0.1</v>
+      </c>
+      <c r="P77">
         <v>19</v>
       </c>
-      <c r="M77">
+      <c r="Q77">
         <v>400</v>
       </c>
-      <c r="O77" t="s">
+      <c r="S77" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="78" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>3</v>
       </c>
@@ -5393,17 +6336,29 @@
       <c r="K78" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L78" s="5">
+      <c r="L78">
+        <v>5.6</v>
+      </c>
+      <c r="M78">
+        <v>5.6</v>
+      </c>
+      <c r="N78" t="s">
+        <v>368</v>
+      </c>
+      <c r="O78">
+        <v>0.1</v>
+      </c>
+      <c r="P78" s="5">
         <v>20</v>
       </c>
-      <c r="M78" s="5">
+      <c r="Q78" s="5">
         <v>600</v>
       </c>
-      <c r="O78" s="5" t="s">
+      <c r="S78" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>3</v>
       </c>
@@ -5436,17 +6391,29 @@
       <c r="K79" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L79" s="5">
+      <c r="L79">
+        <v>5.6</v>
+      </c>
+      <c r="M79">
+        <v>5.6</v>
+      </c>
+      <c r="N79" t="s">
+        <v>368</v>
+      </c>
+      <c r="O79">
+        <v>0.1</v>
+      </c>
+      <c r="P79" s="5">
         <v>20</v>
       </c>
-      <c r="M79" s="5">
+      <c r="Q79" s="5">
         <v>600</v>
       </c>
-      <c r="O79" s="5" t="s">
+      <c r="S79" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>3</v>
       </c>
@@ -5479,17 +6446,29 @@
       <c r="K80" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L80" s="5">
+      <c r="L80">
+        <v>5.6</v>
+      </c>
+      <c r="M80">
+        <v>5.6</v>
+      </c>
+      <c r="N80" t="s">
+        <v>368</v>
+      </c>
+      <c r="O80">
+        <v>0.1</v>
+      </c>
+      <c r="P80" s="5">
         <v>20</v>
       </c>
-      <c r="M80" s="5">
+      <c r="Q80" s="5">
         <v>600</v>
       </c>
-      <c r="O80" s="5" t="s">
+      <c r="S80" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>3</v>
       </c>
@@ -5522,17 +6501,29 @@
       <c r="K81" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L81" s="5">
+      <c r="L81">
+        <v>5.6</v>
+      </c>
+      <c r="M81">
+        <v>5.6</v>
+      </c>
+      <c r="N81" t="s">
+        <v>368</v>
+      </c>
+      <c r="O81">
+        <v>0.1</v>
+      </c>
+      <c r="P81" s="5">
         <v>20</v>
       </c>
-      <c r="M81" s="5">
+      <c r="Q81" s="5">
         <v>600</v>
       </c>
-      <c r="O81" s="5" t="s">
+      <c r="S81" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>3</v>
       </c>
@@ -5565,17 +6556,29 @@
       <c r="K82" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L82" s="5">
+      <c r="L82">
+        <v>5.6</v>
+      </c>
+      <c r="M82">
+        <v>5.6</v>
+      </c>
+      <c r="N82" t="s">
+        <v>368</v>
+      </c>
+      <c r="O82">
+        <v>0.1</v>
+      </c>
+      <c r="P82" s="5">
         <v>20</v>
       </c>
-      <c r="M82" s="5">
+      <c r="Q82" s="5">
         <v>600</v>
       </c>
-      <c r="O82" s="5" t="s">
+      <c r="S82" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>3</v>
       </c>
@@ -5608,17 +6611,29 @@
       <c r="K83" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L83" s="5">
+      <c r="L83">
+        <v>5.6</v>
+      </c>
+      <c r="M83">
+        <v>5.6</v>
+      </c>
+      <c r="N83" t="s">
+        <v>368</v>
+      </c>
+      <c r="O83">
+        <v>0.1</v>
+      </c>
+      <c r="P83" s="5">
         <v>20</v>
       </c>
-      <c r="M83" s="5">
+      <c r="Q83" s="5">
         <v>400</v>
       </c>
-      <c r="O83" s="5" t="s">
+      <c r="S83" s="5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="84" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>3</v>
       </c>
@@ -5651,17 +6666,29 @@
       <c r="K84" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L84" s="5">
+      <c r="L84">
+        <v>5.6</v>
+      </c>
+      <c r="M84">
+        <v>5.6</v>
+      </c>
+      <c r="N84" t="s">
+        <v>368</v>
+      </c>
+      <c r="O84">
+        <v>0.1</v>
+      </c>
+      <c r="P84" s="5">
         <v>20</v>
       </c>
-      <c r="M84" s="5">
+      <c r="Q84" s="5">
         <v>400</v>
       </c>
-      <c r="O84" s="5" t="s">
+      <c r="S84" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="85" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>3</v>
       </c>
@@ -5694,17 +6721,29 @@
       <c r="K85" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L85" s="5">
+      <c r="L85">
+        <v>5.6</v>
+      </c>
+      <c r="M85">
+        <v>5.6</v>
+      </c>
+      <c r="N85" t="s">
+        <v>368</v>
+      </c>
+      <c r="O85">
+        <v>0.1</v>
+      </c>
+      <c r="P85" s="5">
         <v>20</v>
       </c>
-      <c r="M85" s="5">
+      <c r="Q85" s="5">
         <v>400</v>
       </c>
-      <c r="O85" s="5" t="s">
+      <c r="S85" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="86" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>3</v>
       </c>
@@ -5737,17 +6776,29 @@
       <c r="K86" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L86" s="5">
+      <c r="L86">
+        <v>5.6</v>
+      </c>
+      <c r="M86">
+        <v>5.6</v>
+      </c>
+      <c r="N86" t="s">
+        <v>368</v>
+      </c>
+      <c r="O86">
+        <v>0.1</v>
+      </c>
+      <c r="P86" s="5">
         <v>20</v>
       </c>
-      <c r="M86" s="5">
+      <c r="Q86" s="5">
         <v>400</v>
       </c>
-      <c r="O86" s="5" t="s">
+      <c r="S86" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="87" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>3</v>
       </c>
@@ -5780,17 +6831,29 @@
       <c r="K87" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L87" s="5">
+      <c r="L87">
+        <v>5.6</v>
+      </c>
+      <c r="M87">
+        <v>5.6</v>
+      </c>
+      <c r="N87" t="s">
+        <v>368</v>
+      </c>
+      <c r="O87">
+        <v>0.1</v>
+      </c>
+      <c r="P87" s="5">
         <v>20</v>
       </c>
-      <c r="M87" s="5">
+      <c r="Q87" s="5">
         <v>400</v>
       </c>
-      <c r="O87" s="5" t="s">
+      <c r="S87" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -5824,16 +6887,28 @@
         <v>25</v>
       </c>
       <c r="L88">
+        <v>5.6</v>
+      </c>
+      <c r="M88">
+        <v>5.6</v>
+      </c>
+      <c r="N88" t="s">
+        <v>368</v>
+      </c>
+      <c r="O88">
+        <v>0.1</v>
+      </c>
+      <c r="P88">
         <v>18</v>
       </c>
-      <c r="M88">
+      <c r="Q88">
         <v>500</v>
       </c>
-      <c r="O88" t="s">
+      <c r="S88" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -5867,16 +6942,28 @@
         <v>25</v>
       </c>
       <c r="L89">
+        <v>5.6</v>
+      </c>
+      <c r="M89">
+        <v>5.6</v>
+      </c>
+      <c r="N89" t="s">
+        <v>368</v>
+      </c>
+      <c r="O89">
+        <v>0.1</v>
+      </c>
+      <c r="P89">
         <v>18</v>
       </c>
-      <c r="M89">
+      <c r="Q89">
         <v>500</v>
       </c>
-      <c r="O89" t="s">
+      <c r="S89" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -5910,16 +6997,28 @@
         <v>25</v>
       </c>
       <c r="L90">
+        <v>5.6</v>
+      </c>
+      <c r="M90">
+        <v>5.6</v>
+      </c>
+      <c r="N90" t="s">
+        <v>368</v>
+      </c>
+      <c r="O90">
+        <v>0.1</v>
+      </c>
+      <c r="P90">
         <v>18</v>
       </c>
-      <c r="M90">
+      <c r="Q90">
         <v>500</v>
       </c>
-      <c r="O90" t="s">
+      <c r="S90" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -5953,16 +7052,28 @@
         <v>25</v>
       </c>
       <c r="L91">
+        <v>5.6</v>
+      </c>
+      <c r="M91">
+        <v>5.6</v>
+      </c>
+      <c r="N91" t="s">
+        <v>368</v>
+      </c>
+      <c r="O91">
+        <v>0.1</v>
+      </c>
+      <c r="P91">
         <v>18</v>
       </c>
-      <c r="M91">
+      <c r="Q91">
         <v>400</v>
       </c>
-      <c r="O91" t="s">
+      <c r="S91" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -5996,16 +7107,28 @@
         <v>25</v>
       </c>
       <c r="L92">
+        <v>5.6</v>
+      </c>
+      <c r="M92">
+        <v>5.6</v>
+      </c>
+      <c r="N92" t="s">
+        <v>368</v>
+      </c>
+      <c r="O92">
+        <v>0.1</v>
+      </c>
+      <c r="P92">
         <v>18</v>
       </c>
-      <c r="M92">
+      <c r="Q92">
         <v>400</v>
       </c>
-      <c r="O92" t="s">
+      <c r="S92" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -6039,16 +7162,28 @@
         <v>25</v>
       </c>
       <c r="L93">
+        <v>5.6</v>
+      </c>
+      <c r="M93">
+        <v>5.6</v>
+      </c>
+      <c r="N93" t="s">
+        <v>368</v>
+      </c>
+      <c r="O93">
+        <v>0.1</v>
+      </c>
+      <c r="P93">
         <v>18</v>
       </c>
-      <c r="M93">
+      <c r="Q93">
         <v>400</v>
       </c>
-      <c r="O93" t="s">
+      <c r="S93" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>5</v>
       </c>
@@ -6081,17 +7216,29 @@
       <c r="K94" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L94" s="5">
+      <c r="L94">
+        <v>5.6</v>
+      </c>
+      <c r="M94">
+        <v>5.6</v>
+      </c>
+      <c r="N94" t="s">
+        <v>368</v>
+      </c>
+      <c r="O94">
+        <v>0.1</v>
+      </c>
+      <c r="P94" s="5">
         <v>19</v>
       </c>
-      <c r="M94" s="5">
+      <c r="Q94" s="5">
         <v>500</v>
       </c>
-      <c r="O94" s="5" t="s">
+      <c r="S94" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>5</v>
       </c>
@@ -6124,17 +7271,29 @@
       <c r="K95" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L95" s="5">
+      <c r="L95">
+        <v>5.6</v>
+      </c>
+      <c r="M95">
+        <v>5.6</v>
+      </c>
+      <c r="N95" t="s">
+        <v>368</v>
+      </c>
+      <c r="O95">
+        <v>0.1</v>
+      </c>
+      <c r="P95" s="5">
         <v>19</v>
       </c>
-      <c r="M95" s="5">
+      <c r="Q95" s="5">
         <v>500</v>
       </c>
-      <c r="O95" s="5" t="s">
+      <c r="S95" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>5</v>
       </c>
@@ -6167,17 +7326,29 @@
       <c r="K96" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L96" s="5">
+      <c r="L96">
+        <v>5.6</v>
+      </c>
+      <c r="M96">
+        <v>5.6</v>
+      </c>
+      <c r="N96" t="s">
+        <v>368</v>
+      </c>
+      <c r="O96">
+        <v>0.1</v>
+      </c>
+      <c r="P96" s="5">
         <v>19</v>
       </c>
-      <c r="M96" s="5">
+      <c r="Q96" s="5">
         <v>500</v>
       </c>
-      <c r="O96" s="5" t="s">
+      <c r="S96" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="97" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>5</v>
       </c>
@@ -6210,17 +7381,29 @@
       <c r="K97" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L97" s="5">
+      <c r="L97">
+        <v>5.6</v>
+      </c>
+      <c r="M97">
+        <v>5.6</v>
+      </c>
+      <c r="N97" t="s">
+        <v>368</v>
+      </c>
+      <c r="O97">
+        <v>0.1</v>
+      </c>
+      <c r="P97" s="5">
         <v>19</v>
       </c>
-      <c r="M97" s="5">
+      <c r="Q97" s="5">
         <v>500</v>
       </c>
-      <c r="O97" s="5" t="s">
+      <c r="S97" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>5</v>
       </c>
@@ -6253,17 +7436,29 @@
       <c r="K98" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L98" s="5">
+      <c r="L98">
+        <v>5.6</v>
+      </c>
+      <c r="M98">
+        <v>5.6</v>
+      </c>
+      <c r="N98" t="s">
+        <v>368</v>
+      </c>
+      <c r="O98">
+        <v>0.1</v>
+      </c>
+      <c r="P98" s="5">
         <v>19</v>
       </c>
-      <c r="M98" s="5">
+      <c r="Q98" s="5">
         <v>400</v>
       </c>
-      <c r="O98" s="5" t="s">
+      <c r="S98" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="99" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>5</v>
       </c>
@@ -6296,17 +7491,29 @@
       <c r="K99" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L99" s="5">
+      <c r="L99">
+        <v>5.6</v>
+      </c>
+      <c r="M99">
+        <v>5.6</v>
+      </c>
+      <c r="N99" t="s">
+        <v>368</v>
+      </c>
+      <c r="O99">
+        <v>0.1</v>
+      </c>
+      <c r="P99" s="5">
         <v>19</v>
       </c>
-      <c r="M99" s="5">
+      <c r="Q99" s="5">
         <v>400</v>
       </c>
-      <c r="O99" s="5" t="s">
+      <c r="S99" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="100" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>5</v>
       </c>
@@ -6339,17 +7546,29 @@
       <c r="K100" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L100" s="5">
+      <c r="L100">
+        <v>5.6</v>
+      </c>
+      <c r="M100">
+        <v>5.6</v>
+      </c>
+      <c r="N100" t="s">
+        <v>368</v>
+      </c>
+      <c r="O100">
+        <v>0.1</v>
+      </c>
+      <c r="P100" s="5">
         <v>19</v>
       </c>
-      <c r="M100" s="5">
+      <c r="Q100" s="5">
         <v>400</v>
       </c>
-      <c r="O100" s="5" t="s">
+      <c r="S100" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="101" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>5</v>
       </c>
@@ -6382,17 +7601,29 @@
       <c r="K101" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L101" s="5">
+      <c r="L101">
+        <v>5.6</v>
+      </c>
+      <c r="M101">
+        <v>5.6</v>
+      </c>
+      <c r="N101" t="s">
+        <v>368</v>
+      </c>
+      <c r="O101">
+        <v>0.1</v>
+      </c>
+      <c r="P101" s="5">
         <v>19</v>
       </c>
-      <c r="M101" s="5">
+      <c r="Q101" s="5">
         <v>400</v>
       </c>
-      <c r="O101" s="5" t="s">
+      <c r="S101" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -6426,16 +7657,28 @@
         <v>25</v>
       </c>
       <c r="L102">
+        <v>5.6</v>
+      </c>
+      <c r="M102">
+        <v>5.6</v>
+      </c>
+      <c r="N102" t="s">
+        <v>368</v>
+      </c>
+      <c r="O102">
+        <v>0.1</v>
+      </c>
+      <c r="P102">
         <v>20</v>
       </c>
-      <c r="M102">
+      <c r="Q102">
         <v>600</v>
       </c>
-      <c r="O102" t="s">
+      <c r="S102" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>6</v>
       </c>
@@ -6469,16 +7712,28 @@
         <v>25</v>
       </c>
       <c r="L103">
+        <v>5.6</v>
+      </c>
+      <c r="M103">
+        <v>5.6</v>
+      </c>
+      <c r="N103" t="s">
+        <v>368</v>
+      </c>
+      <c r="O103">
+        <v>0.1</v>
+      </c>
+      <c r="P103">
         <v>20</v>
       </c>
-      <c r="M103">
+      <c r="Q103">
         <v>600</v>
       </c>
-      <c r="O103" t="s">
+      <c r="S103" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -6512,16 +7767,28 @@
         <v>25</v>
       </c>
       <c r="L104">
+        <v>5.6</v>
+      </c>
+      <c r="M104">
+        <v>5.6</v>
+      </c>
+      <c r="N104" t="s">
+        <v>368</v>
+      </c>
+      <c r="O104">
+        <v>0.1</v>
+      </c>
+      <c r="P104">
         <v>20</v>
       </c>
-      <c r="M104">
+      <c r="Q104">
         <v>600</v>
       </c>
-      <c r="O104" t="s">
+      <c r="S104" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -6555,16 +7822,28 @@
         <v>25</v>
       </c>
       <c r="L105">
+        <v>5.6</v>
+      </c>
+      <c r="M105">
+        <v>5.6</v>
+      </c>
+      <c r="N105" t="s">
+        <v>368</v>
+      </c>
+      <c r="O105">
+        <v>0.1</v>
+      </c>
+      <c r="P105">
         <v>20</v>
       </c>
-      <c r="M105">
+      <c r="Q105">
         <v>600</v>
       </c>
-      <c r="O105" t="s">
+      <c r="S105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>6</v>
       </c>
@@ -6598,16 +7877,28 @@
         <v>25</v>
       </c>
       <c r="L106">
+        <v>5.6</v>
+      </c>
+      <c r="M106">
+        <v>5.6</v>
+      </c>
+      <c r="N106" t="s">
+        <v>368</v>
+      </c>
+      <c r="O106">
+        <v>0.1</v>
+      </c>
+      <c r="P106">
         <v>20</v>
       </c>
-      <c r="M106">
+      <c r="Q106">
         <v>600</v>
       </c>
-      <c r="O106" t="s">
+      <c r="S106" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>6</v>
       </c>
@@ -6641,16 +7932,28 @@
         <v>25</v>
       </c>
       <c r="L107">
+        <v>5.6</v>
+      </c>
+      <c r="M107">
+        <v>5.6</v>
+      </c>
+      <c r="N107" t="s">
+        <v>368</v>
+      </c>
+      <c r="O107">
+        <v>0.1</v>
+      </c>
+      <c r="P107">
         <v>20</v>
       </c>
-      <c r="M107">
+      <c r="Q107">
         <v>600</v>
       </c>
-      <c r="O107" t="s">
+      <c r="S107" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>6</v>
       </c>
@@ -6684,16 +7987,28 @@
         <v>25</v>
       </c>
       <c r="L108">
+        <v>5.6</v>
+      </c>
+      <c r="M108">
+        <v>5.6</v>
+      </c>
+      <c r="N108" t="s">
+        <v>368</v>
+      </c>
+      <c r="O108">
+        <v>0.1</v>
+      </c>
+      <c r="P108">
         <v>179</v>
       </c>
-      <c r="M108">
+      <c r="Q108">
         <v>600</v>
       </c>
-      <c r="O108" t="s">
+      <c r="S108" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -6727,16 +8042,28 @@
         <v>25</v>
       </c>
       <c r="L109">
+        <v>5.6</v>
+      </c>
+      <c r="M109">
+        <v>5.6</v>
+      </c>
+      <c r="N109" t="s">
+        <v>368</v>
+      </c>
+      <c r="O109">
+        <v>0.1</v>
+      </c>
+      <c r="P109">
         <v>179</v>
       </c>
-      <c r="M109">
+      <c r="Q109">
         <v>600</v>
       </c>
-      <c r="O109" t="s">
+      <c r="S109" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -6770,16 +8097,28 @@
         <v>25</v>
       </c>
       <c r="L110">
+        <v>5.6</v>
+      </c>
+      <c r="M110">
+        <v>5.6</v>
+      </c>
+      <c r="N110" t="s">
+        <v>368</v>
+      </c>
+      <c r="O110">
+        <v>0.1</v>
+      </c>
+      <c r="P110">
         <v>179</v>
       </c>
-      <c r="M110">
+      <c r="Q110">
         <v>600</v>
       </c>
-      <c r="O110" t="s">
+      <c r="S110" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -6813,16 +8152,28 @@
         <v>25</v>
       </c>
       <c r="L111">
+        <v>5.6</v>
+      </c>
+      <c r="M111">
+        <v>5.6</v>
+      </c>
+      <c r="N111" t="s">
+        <v>368</v>
+      </c>
+      <c r="O111">
+        <v>0.1</v>
+      </c>
+      <c r="P111">
         <v>179</v>
       </c>
-      <c r="M111">
+      <c r="Q111">
         <v>600</v>
       </c>
-      <c r="O111" t="s">
+      <c r="S111" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -6856,16 +8207,28 @@
         <v>25</v>
       </c>
       <c r="L112">
+        <v>5.6</v>
+      </c>
+      <c r="M112">
+        <v>5.6</v>
+      </c>
+      <c r="N112" t="s">
+        <v>368</v>
+      </c>
+      <c r="O112">
+        <v>0.1</v>
+      </c>
+      <c r="P112">
         <v>20</v>
       </c>
-      <c r="M112">
+      <c r="Q112">
         <v>400</v>
       </c>
-      <c r="O112" t="s">
+      <c r="S112" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -6899,16 +8262,28 @@
         <v>25</v>
       </c>
       <c r="L113">
+        <v>5.6</v>
+      </c>
+      <c r="M113">
+        <v>5.6</v>
+      </c>
+      <c r="N113" t="s">
+        <v>368</v>
+      </c>
+      <c r="O113">
+        <v>0.1</v>
+      </c>
+      <c r="P113">
         <v>20</v>
       </c>
-      <c r="M113">
+      <c r="Q113">
         <v>400</v>
       </c>
-      <c r="O113" t="s">
+      <c r="S113" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -6942,16 +8317,28 @@
         <v>25</v>
       </c>
       <c r="L114">
+        <v>5.6</v>
+      </c>
+      <c r="M114">
+        <v>5.6</v>
+      </c>
+      <c r="N114" t="s">
+        <v>368</v>
+      </c>
+      <c r="O114">
+        <v>0.1</v>
+      </c>
+      <c r="P114">
         <v>20</v>
       </c>
-      <c r="M114">
+      <c r="Q114">
         <v>400</v>
       </c>
-      <c r="O114" t="s">
+      <c r="S114" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -6985,16 +8372,28 @@
         <v>25</v>
       </c>
       <c r="L115">
+        <v>5.6</v>
+      </c>
+      <c r="M115">
+        <v>5.6</v>
+      </c>
+      <c r="N115" t="s">
+        <v>368</v>
+      </c>
+      <c r="O115">
+        <v>0.1</v>
+      </c>
+      <c r="P115">
         <v>20</v>
       </c>
-      <c r="M115">
+      <c r="Q115">
         <v>400</v>
       </c>
-      <c r="O115" t="s">
+      <c r="S115" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>6</v>
       </c>
@@ -7028,16 +8427,28 @@
         <v>25</v>
       </c>
       <c r="L116">
+        <v>5.6</v>
+      </c>
+      <c r="M116">
+        <v>5.6</v>
+      </c>
+      <c r="N116" t="s">
+        <v>368</v>
+      </c>
+      <c r="O116">
+        <v>0.1</v>
+      </c>
+      <c r="P116">
         <v>20</v>
       </c>
-      <c r="M116">
+      <c r="Q116">
         <v>400</v>
       </c>
-      <c r="O116" t="s">
+      <c r="S116" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -7071,16 +8482,28 @@
         <v>25</v>
       </c>
       <c r="L117">
+        <v>5.6</v>
+      </c>
+      <c r="M117">
+        <v>5.6</v>
+      </c>
+      <c r="N117" t="s">
+        <v>368</v>
+      </c>
+      <c r="O117">
+        <v>0.1</v>
+      </c>
+      <c r="P117">
         <v>20</v>
       </c>
-      <c r="M117">
+      <c r="Q117">
         <v>400</v>
       </c>
-      <c r="O117" t="s">
+      <c r="S117" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>6</v>
       </c>
@@ -7114,16 +8537,28 @@
         <v>25</v>
       </c>
       <c r="L118">
+        <v>5.6</v>
+      </c>
+      <c r="M118">
+        <v>5.6</v>
+      </c>
+      <c r="N118" t="s">
+        <v>368</v>
+      </c>
+      <c r="O118">
+        <v>0.1</v>
+      </c>
+      <c r="P118">
         <v>179</v>
       </c>
-      <c r="M118">
+      <c r="Q118">
         <v>400</v>
       </c>
-      <c r="O118" t="s">
+      <c r="S118" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -7157,16 +8592,28 @@
         <v>25</v>
       </c>
       <c r="L119">
+        <v>5.6</v>
+      </c>
+      <c r="M119">
+        <v>5.6</v>
+      </c>
+      <c r="N119" t="s">
+        <v>368</v>
+      </c>
+      <c r="O119">
+        <v>0.1</v>
+      </c>
+      <c r="P119">
         <v>179</v>
       </c>
-      <c r="M119">
+      <c r="Q119">
         <v>400</v>
       </c>
-      <c r="O119" t="s">
+      <c r="S119" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>6</v>
       </c>
@@ -7200,16 +8647,28 @@
         <v>25</v>
       </c>
       <c r="L120">
+        <v>5.6</v>
+      </c>
+      <c r="M120">
+        <v>5.6</v>
+      </c>
+      <c r="N120" t="s">
+        <v>368</v>
+      </c>
+      <c r="O120">
+        <v>0.1</v>
+      </c>
+      <c r="P120">
         <v>179</v>
       </c>
-      <c r="M120">
+      <c r="Q120">
         <v>400</v>
       </c>
-      <c r="O120" t="s">
+      <c r="S120" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -7243,12 +8702,24 @@
         <v>25</v>
       </c>
       <c r="L121">
+        <v>5.6</v>
+      </c>
+      <c r="M121">
+        <v>5.6</v>
+      </c>
+      <c r="N121" t="s">
+        <v>368</v>
+      </c>
+      <c r="O121">
+        <v>0.1</v>
+      </c>
+      <c r="P121">
         <v>179</v>
       </c>
-      <c r="M121">
+      <c r="Q121">
         <v>400</v>
       </c>
-      <c r="O121" t="s">
+      <c r="S121" t="s">
         <v>127</v>
       </c>
     </row>
